--- a/KatalonData/EmailTextToPay/ManualEntry_Upgrade.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_Upgrade.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="154">
   <si>
     <t>Result</t>
   </si>
@@ -319,12 +319,193 @@
   </si>
   <si>
     <t>Mon Jul 13 18:54:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:07:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:08:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:08:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:09:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:10:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:10:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:11:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:12:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:13:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:13:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:14:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:23:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:23:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:24:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:25:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:26:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:28:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:29:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:29:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:30:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:32:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:32:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:33:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:34:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:34:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:35:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:37:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:38:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:39:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:40:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:40:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:41:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:42:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:42:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:43:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:44:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:45:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:47:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:49:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:49:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:50:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:51:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:52:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:52:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:53:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:54:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:54:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:55:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:56:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:57:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:59:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 10:00:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 10:00:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 10:01:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 10:02:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 10:02:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 10:03:39 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -845,29 +1026,29 @@
   <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.36328125" style="19" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="31.26953125" style="4" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.08984375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="25.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="5.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="11.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="15" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="15" width="14.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="10.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="10.81640625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="13.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="15.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="24" max="28" width="8.7265625" style="6" collapsed="1"/>
-    <col min="29" max="16384" width="8.7265625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="19" width="15.36328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="4" width="31.26953125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="8.08984375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="25.1796875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="5.81640625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
+    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="11.90625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="15.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
+    <col min="14" max="15" customWidth="true" style="6" width="14.453125" collapsed="true"/>
+    <col min="16" max="16" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="6" width="10.6328125" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="6" width="10.81640625" collapsed="true"/>
+    <col min="21" max="21" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
+    <col min="22" max="22" customWidth="true" style="6" width="13.6328125" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="6" width="15.453125" collapsed="true"/>
+    <col min="24" max="28" style="6" width="8.7265625" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.25">
@@ -961,7 +1142,7 @@
         <v>53</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>42</v>
@@ -1007,7 +1188,7 @@
         <v>53</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>43</v>
@@ -1034,7 +1215,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>44</v>
@@ -1063,7 +1244,7 @@
         <v>53</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>47</v>
@@ -1116,7 +1297,7 @@
         <v>53</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>45</v>
@@ -1169,7 +1350,7 @@
         <v>53</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>46</v>
@@ -1225,7 +1406,7 @@
         <v>53</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>39</v>
@@ -1257,7 +1438,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>40</v>
@@ -1286,7 +1467,7 @@
         <v>53</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>41</v>
@@ -1315,7 +1496,7 @@
         <v>53</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>67</v>
@@ -1374,7 +1555,7 @@
         <v>53</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
@@ -1450,35 +1631,35 @@
   <dimension ref="A1:AC13"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="36" style="11" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
-    <col min="5" max="5" width="25.1796875" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="13.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="17" width="8.7265625" style="6" collapsed="1"/>
-    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="9.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="10.81640625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="8.7265625" style="6" collapsed="1"/>
-    <col min="22" max="22" width="10.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="6" style="6" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="8.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
-    <col min="30" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="11" width="36.0" collapsed="true"/>
+    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="6" width="25.1796875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="6" width="13.453125" collapsed="true"/>
+    <col min="16" max="17" style="6" width="8.7265625" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="6" width="9.54296875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="6" width="10.81640625" collapsed="true"/>
+    <col min="21" max="21" style="6" width="8.7265625" collapsed="true"/>
+    <col min="22" max="22" customWidth="true" style="6" width="10.26953125" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="6" width="6.0" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="6" width="8.453125" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="28" max="28" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
+    <col min="30" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -1575,7 +1756,7 @@
         <v>53</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>48</v>
@@ -1623,7 +1804,7 @@
         <v>53</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>20</v>
@@ -1641,7 +1822,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>19</v>
@@ -1658,10 +1839,10 @@
     </row>
     <row r="5" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>27</v>
@@ -1706,10 +1887,10 @@
     </row>
     <row r="6" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>28</v>
@@ -1739,7 +1920,7 @@
         <v>53</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>30</v>
@@ -1771,7 +1952,7 @@
         <v>53</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>21</v>
@@ -1803,7 +1984,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>22</v>
@@ -1829,7 +2010,7 @@
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>23</v>
@@ -1882,7 +2063,7 @@
         <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>29</v>
@@ -1917,7 +2098,7 @@
         <v>53</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>69</v>
@@ -1967,8 +2148,8 @@
       <c r="A13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B13" t="s">
-        <v>93</v>
+      <c r="B13" t="s" s="6">
+        <v>153</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>70</v>
